--- a/atomone.xlsx
+++ b/atomone.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="356">
   <si>
     <t>delegator_address</t>
   </si>
@@ -22,25 +22,43 @@
     <t>atone1q2833t82zthataz0v6zracejyu7xfqh7mu2sw4</t>
   </si>
   <si>
-    <t>288223872</t>
+    <t>320423872</t>
   </si>
   <si>
     <t>atone1qvcy2gqxrdgnnypgsjcr2xz57lf4cs6nyslal2</t>
   </si>
   <si>
-    <t>12092500000</t>
+    <t>13879700000</t>
+  </si>
+  <si>
+    <t>atone1qdj33jvvj67vyyhh454q6u7u8scplhvq8l3ren</t>
+  </si>
+  <si>
+    <t>300066965</t>
   </si>
   <si>
     <t>atone1qs4eqtc0f28943s9q8jzcncr5pkmcgkf07lenq</t>
   </si>
   <si>
-    <t>284600000</t>
+    <t>289700000</t>
   </si>
   <si>
     <t>atone1q648z887yenz2gxkq4msa252nvp427tfsvh8hu</t>
   </si>
   <si>
-    <t>1527911947</t>
+    <t>1682192753</t>
+  </si>
+  <si>
+    <t>atone1qm0q9ec5ylrgz2sz78j53xnrfcsse74a23ad2g</t>
+  </si>
+  <si>
+    <t>380143640</t>
+  </si>
+  <si>
+    <t>atone1quun3k4usk4gyad8drug4j9rmsmng30as3aty6</t>
+  </si>
+  <si>
+    <t>1000000000</t>
   </si>
   <si>
     <t>atone1pz0gys67zv6dl0g69dree3yees48plzun5xcek</t>
@@ -49,6 +67,18 @@
     <t>490000000</t>
   </si>
   <si>
+    <t>atone1p6s3nqc8rr02j5n9qhtmt7zkf4ur2j0vf04p5p</t>
+  </si>
+  <si>
+    <t>468938493</t>
+  </si>
+  <si>
+    <t>atone1zxprgrhmf6zwkvrwmk08kgtlhu4ptk6sry58r3</t>
+  </si>
+  <si>
+    <t>1000310644</t>
+  </si>
+  <si>
     <t>atone1zgs5nnwhpxg4sjyw7xerm4humluxua90ejay73</t>
   </si>
   <si>
@@ -61,16 +91,19 @@
     <t>450000000</t>
   </si>
   <si>
+    <t>atone1zlmdnd2uem5kxx7rdmkfnq2wl5cvfjxuktnvsh</t>
+  </si>
+  <si>
     <t>atone1rxwnxskx7w9jjecfzjve35juw3qxughs9nwku7</t>
   </si>
   <si>
-    <t>1100000000</t>
+    <t>1110000000</t>
   </si>
   <si>
     <t>atone1rf0s9p99t3m0vnwcf0jy98hwedlrul90tsvp4s</t>
   </si>
   <si>
-    <t>1805012486</t>
+    <t>4003480821</t>
   </si>
   <si>
     <t>atone1r2nujddqfxvw3nuvdfgsnskxgrdhpfz76a0msu</t>
@@ -88,7 +121,7 @@
     <t>atone1rhyz30vg0c6ed69rmz43h35wn92ucksrclvndw</t>
   </si>
   <si>
-    <t>2205912322</t>
+    <t>2427924513</t>
   </si>
   <si>
     <t>atone1rhgsg2qedccgwrpws524tagm4v7rlpdre0m4kz</t>
@@ -97,6 +130,24 @@
     <t>28216547118</t>
   </si>
   <si>
+    <t>atone1rcv6x4e0pddxulx7525uf468ttk9pedm3967f3</t>
+  </si>
+  <si>
+    <t>724135764</t>
+  </si>
+  <si>
+    <t>atone1yq7n7f6ekn8rcxmlc033ea58kw5z0ly3w4ay8w</t>
+  </si>
+  <si>
+    <t>1000004421</t>
+  </si>
+  <si>
+    <t>atone1yyxsxmf635pxvm0hlfucdegprh55xsxpdc56fe</t>
+  </si>
+  <si>
+    <t>300010026</t>
+  </si>
+  <si>
     <t>atone1yyvdwarlwt4sz6qslzs5sx5jlzu6guajpduunn</t>
   </si>
   <si>
@@ -106,13 +157,13 @@
     <t>atone1ysthp74n2wxt4flmzyxrhza8rvxzr9mclfes0v</t>
   </si>
   <si>
-    <t>500017077</t>
+    <t>707419783</t>
   </si>
   <si>
     <t>atone1ykyk43nxapm48n60ft0sr8ndrg8deu9p2d5ckt</t>
   </si>
   <si>
-    <t>2002297678</t>
+    <t>2330297678</t>
   </si>
   <si>
     <t>atone19g9flltdr2ahajrkefdqxc34h5uc532d4xgk5s</t>
@@ -130,7 +181,7 @@
     <t>atone19dej9nex9sj3424eernwjs83pw75rt3k25hv90</t>
   </si>
   <si>
-    <t>225000000</t>
+    <t>276000000</t>
   </si>
   <si>
     <t>atone193d2qsuk25e9mx0quan2msl2y9fqtt0gw6vxe9</t>
@@ -142,7 +193,31 @@
     <t>atone19jhlpyjx3p4kqh347323azjuhnnew95r0a5z2u</t>
   </si>
   <si>
-    <t>224000000</t>
+    <t>271800061</t>
+  </si>
+  <si>
+    <t>atone195uet0szm7hwaps2k99ywscsdl7hjcy8k7qeuh</t>
+  </si>
+  <si>
+    <t>300080126</t>
+  </si>
+  <si>
+    <t>atone194sg0pj6p5nk7dpnuh7wwm0evlwhw8zyswmmdd</t>
+  </si>
+  <si>
+    <t>300080040</t>
+  </si>
+  <si>
+    <t>atone19uga3gpvacvlyuv2mf027n4xqrv4tssexz3wx7</t>
+  </si>
+  <si>
+    <t>461408431</t>
+  </si>
+  <si>
+    <t>atone1xs7hps4auv5ksa9a2vuk90v07agx8nlxn6g8xa</t>
+  </si>
+  <si>
+    <t>285000000</t>
   </si>
   <si>
     <t>atone18gd7nsv2qrx9rv8n0gh37l0x8qmwnrhad9r40u</t>
@@ -151,22 +226,28 @@
     <t>1722000000</t>
   </si>
   <si>
+    <t>atone18nf84jgwkqypaplz45xyf3yegpu4vvhznf9gn4</t>
+  </si>
+  <si>
+    <t>250872257</t>
+  </si>
+  <si>
     <t>atone185fkw70ntyc0vlvrf30grsxurfw2d7cplyp8ep</t>
   </si>
   <si>
-    <t>300824166</t>
+    <t>468824166</t>
   </si>
   <si>
     <t>atone1850rdjq4sf488sad4qsj64sj2s8h53z0hhu7q7</t>
   </si>
   <si>
-    <t>999962488</t>
+    <t>1000002488</t>
   </si>
   <si>
     <t>atone18crvw4qkw8ju6s9jqyw6w3wx5ghh3unvd6zgw5</t>
   </si>
   <si>
-    <t>251796243</t>
+    <t>449426243</t>
   </si>
   <si>
     <t>atone18ank35aua8ftetpmvcsxwdqy4pheltee3wzc2f</t>
@@ -175,16 +256,25 @@
     <t>218000000</t>
   </si>
   <si>
+    <t>atone18l3v435q04cmxn0ec45r3vwxdfl3har3ntywp2</t>
+  </si>
+  <si>
     <t>atone1gzwmgc096jgunp47tnn7j7ulzgc97ce8s82dzw</t>
   </si>
   <si>
-    <t>1358694210</t>
+    <t>1495890303</t>
+  </si>
+  <si>
+    <t>atone1gxa40yjrgrlt2ffqka8cgycxnhlq9kd2f4u93y</t>
+  </si>
+  <si>
+    <t>1000330102</t>
   </si>
   <si>
     <t>atone1gd6twrfw7p04797dznh0u98q9ykc7d240qac6a</t>
   </si>
   <si>
-    <t>202988690</t>
+    <t>217960229</t>
   </si>
   <si>
     <t>atone1g37mcad2p7w4d8zes77mly0tawrmhvamjkdp22</t>
@@ -196,7 +286,7 @@
     <t>atone1gn6w54uge5drhx0gskdgva4372d8guxh0wyz6n</t>
   </si>
   <si>
-    <t>445000000</t>
+    <t>683000000</t>
   </si>
   <si>
     <t>atone1gnasfq4qq9kuwphp7ytq50pg6f4pzqs4gqu73d</t>
@@ -208,7 +298,7 @@
     <t>atone1frwewwrswegyuxsz800zeaqesq5k678xe5hd9p</t>
   </si>
   <si>
-    <t>570900000</t>
+    <t>850000000</t>
   </si>
   <si>
     <t>atone1f9dge7nrtrlxg24qekrwk24nxzmzlappuw8q39</t>
@@ -220,13 +310,13 @@
     <t>atone1f8qxs3n4pstp3ddfzt7773w9wl3c6c04nj7r0d</t>
   </si>
   <si>
-    <t>300824508</t>
+    <t>468824508</t>
   </si>
   <si>
     <t>atone1f44qd2yw4f007dqddltptaqyqly9qs05n8edum</t>
   </si>
   <si>
-    <t>220000041</t>
+    <t>246000041</t>
   </si>
   <si>
     <t>atone1fcygwdcfwdnt8gpuv0rr5j6llnexsw6655j42g</t>
@@ -238,7 +328,7 @@
     <t>atone1f6w3gudyw02vg7jql2kqyte9us8qa5kxfpkwva</t>
   </si>
   <si>
-    <t>335164791</t>
+    <t>500164791</t>
   </si>
   <si>
     <t>atone1fud5k0utxxjm27je5t72h82tyten72acpns7n3</t>
@@ -247,7 +337,13 @@
     <t>atone12pjgwmk672r98fhjrpxg9xz2j29vmu9r472x4s</t>
   </si>
   <si>
-    <t>974000000</t>
+    <t>1067098314</t>
+  </si>
+  <si>
+    <t>atone12ydrj8eml4wq2cvva7s502ge2w5u7qh5n736c9</t>
+  </si>
+  <si>
+    <t>5401316174</t>
   </si>
   <si>
     <t>atone122xq6xe80jk5zkhul6zzh80n2k69yr2eh34ht4</t>
@@ -259,13 +355,13 @@
     <t>atone12v736nuytn9rjl5dpqtfxzdg40vtlwqqwcx2h8</t>
   </si>
   <si>
-    <t>558466316</t>
+    <t>618151136</t>
   </si>
   <si>
     <t>atone12dz0vh9gk50wsjc7jvefs7l8fafraalc7stqkl</t>
   </si>
   <si>
-    <t>558463588</t>
+    <t>618145609</t>
   </si>
   <si>
     <t>atone124rxmmffm329znr5ww8tats35gjq2jzj3m2f8e</t>
@@ -274,10 +370,22 @@
     <t>500200000</t>
   </si>
   <si>
+    <t>atone12c2f2rd0v27ceds29pz4whpumqpxnhk7udqn5s</t>
+  </si>
+  <si>
+    <t>675750000</t>
+  </si>
+  <si>
+    <t>atone12c6y9dm97r05cu2ewjjw0gm4f6y0pnsm3nwau7</t>
+  </si>
+  <si>
+    <t>214000000</t>
+  </si>
+  <si>
     <t>atone12el8k6fz3n80mv2czz6apdxplsnpxznawsllcl</t>
   </si>
   <si>
-    <t>5385500000</t>
+    <t>6000000000</t>
   </si>
   <si>
     <t>atone1tyu6854q0vlsqpmvaasr9043cwfrtmu4494s50</t>
@@ -286,16 +394,43 @@
     <t>201000000</t>
   </si>
   <si>
+    <t>atone1tg3fa0td5gkzvq94vjefhxu7llyqj3mvnqtm9l</t>
+  </si>
+  <si>
+    <t>739000000</t>
+  </si>
+  <si>
+    <t>atone1td0nm484l83c4yp3pna9h03jg34wfwrz04weml</t>
+  </si>
+  <si>
+    <t>294001118</t>
+  </si>
+  <si>
     <t>atone1tk9ecdjc59ek3r3dsqe83026jxvtlr0kst3j2z</t>
   </si>
   <si>
-    <t>300382015</t>
+    <t>468382015</t>
+  </si>
+  <si>
+    <t>atone1t7gdzehwj5snn8hqg97dejuzj7eym42azeyswe</t>
+  </si>
+  <si>
+    <t>300080109</t>
+  </si>
+  <si>
+    <t>atone1vv82mgf9s2uvjre4449ugr3ljyfqdpzh2puwrt</t>
+  </si>
+  <si>
+    <t>atone1vw9zdq0yxuazrsa5hsksd5apdsme2etvr8fgd2</t>
+  </si>
+  <si>
+    <t>300080272</t>
   </si>
   <si>
     <t>atone1vkngvnelw4tgahyn20sr0kvk9jq8wrfefvh2lr</t>
   </si>
   <si>
-    <t>211810767</t>
+    <t>265041313</t>
   </si>
   <si>
     <t>atone1dqf5rg4kccq558f29qa02wurmcmrapchm6xkhf</t>
@@ -307,10 +442,13 @@
     <t>atone1d93ggvd6t3qnna3w280ax9g6j9jzr69envan9n</t>
   </si>
   <si>
+    <t>245000000</t>
+  </si>
+  <si>
     <t>atone1dxlzv3nym93x72t6d5rtaqzre7skke3nk3nzwg</t>
   </si>
   <si>
-    <t>681112818</t>
+    <t>1000009071</t>
   </si>
   <si>
     <t>atone1d27jtvp26d2ul4lwy6th9mqmwxvp68pje4lzj2</t>
@@ -322,10 +460,22 @@
     <t>atone1ddg9tjkf0vmd3t2mdqpxk2pkk6zssvduphf7js</t>
   </si>
   <si>
+    <t>atone1d06u6y3uaud037prwuhyc6r4g0znyc9rtjcuzt</t>
+  </si>
+  <si>
+    <t>1005413937</t>
+  </si>
+  <si>
+    <t>atone1d076ek2e7m24jskmlgamv7kut7df892tcsnle9</t>
+  </si>
+  <si>
+    <t>312000000</t>
+  </si>
+  <si>
     <t>atone1dn54g3fpsp853jmux297fpj89uufn3zxgmuqfh</t>
   </si>
   <si>
-    <t>238586659</t>
+    <t>248592319</t>
   </si>
   <si>
     <t>atone1dkqem467z8l7vjktx7ldg93r82e056qs0m3skm</t>
@@ -334,19 +484,40 @@
     <t>atone1de88sp2h3955ktrjgnm0jkhy8dttsgdzmnu3s9</t>
   </si>
   <si>
-    <t>425162375</t>
+    <t>525162375</t>
+  </si>
+  <si>
+    <t>atone1wpxr45kyyzzuaz6s8h7g33d0sjxu9d00u0kzxs</t>
+  </si>
+  <si>
+    <t>533000000</t>
   </si>
   <si>
     <t>atone1w9gcxhaxj8f0rjlkwwu36e7elj9aqmj3txzhp8</t>
   </si>
   <si>
-    <t>208000000</t>
-  </si>
-  <si>
-    <t>atone1wkep6k06rqh2vls8t5q2jjkdn4z803alu5e235</t>
-  </si>
-  <si>
-    <t>400211897</t>
+    <t>atone1wxv8jnx4tnr5rr5uwnx05g3s74tcpzaj06y83e</t>
+  </si>
+  <si>
+    <t>2237969553</t>
+  </si>
+  <si>
+    <t>atone1wd0867jyazkkuepypfsupnunygv38cg8dn7kmp</t>
+  </si>
+  <si>
+    <t>468939022</t>
+  </si>
+  <si>
+    <t>atone1wwg9r2s99ca9esdvugg6w03zlatv6kprjjhtt2</t>
+  </si>
+  <si>
+    <t>290000000</t>
+  </si>
+  <si>
+    <t>atone1wn33dw4upqvtgz70xg264j68026426ahzv9gpn</t>
+  </si>
+  <si>
+    <t>302000000</t>
   </si>
   <si>
     <t>atone1w64nk0hmjelradw68twzs8zngk253y3g27s0sr</t>
@@ -355,22 +526,37 @@
     <t>550000000</t>
   </si>
   <si>
-    <t>atone10yp8ey37pjt4y5cr6nl2dstqjyz9f5k93nqlx2</t>
-  </si>
-  <si>
-    <t>401190000</t>
+    <t>atone1watcl6uwglas3zumlkz8se0j33zzt6sknd2lxd</t>
+  </si>
+  <si>
+    <t>282000000</t>
+  </si>
+  <si>
+    <t>atone10rgr9c9qwzpyl3yv9zgtprtskmzuzs06tx7u6w</t>
   </si>
   <si>
     <t>atone10gzg69ktz2ku6swm400ghtpfj77u9hg7ua0t55</t>
   </si>
   <si>
-    <t>206249381</t>
+    <t>227076162</t>
   </si>
   <si>
     <t>atone10guvn4243qg2l8ey8gy9zwttz6v23232k9wm5k</t>
   </si>
   <si>
-    <t>1492234585</t>
+    <t>1642234585</t>
+  </si>
+  <si>
+    <t>atone1srrk9qyuc3255u7h8zk78n5pvu3vatt96ejuks</t>
+  </si>
+  <si>
+    <t>1000002783</t>
+  </si>
+  <si>
+    <t>atone1snydm4jj9j9fd8vyxw6sansv52653de820xnxt</t>
+  </si>
+  <si>
+    <t>1862084711</t>
   </si>
   <si>
     <t>atone1sn0gq7jlk5cscurvnsrlxc644p2dkwq56anjm7</t>
@@ -379,16 +565,34 @@
     <t>52746366457</t>
   </si>
   <si>
+    <t>atone1s4szs2h38m5g20c7cwg9nve6whww4e09tvt9xz</t>
+  </si>
+  <si>
+    <t>300067567</t>
+  </si>
+  <si>
     <t>atone1su0p2tyhph4hv6ud22c057rz3f8gfvrsly8kyy</t>
   </si>
   <si>
-    <t>297055618</t>
+    <t>327052057</t>
+  </si>
+  <si>
+    <t>atone1sltq5xnhhh02zelpphpkqqfy48w7rg47s9zjr6</t>
+  </si>
+  <si>
+    <t>555500000</t>
   </si>
   <si>
     <t>atone13zzlsjnauafxz764nvj6mgagrkt5vke37jskxy</t>
   </si>
   <si>
-    <t>1112163228</t>
+    <t>1171903798</t>
+  </si>
+  <si>
+    <t>atone13g25c4rmcyq2nxhpu00nke5u0puld50gn0as9h</t>
+  </si>
+  <si>
+    <t>280355742</t>
   </si>
   <si>
     <t>atone130umlsvuey3ss03p9pnmnww4mx3zta4skzath6</t>
@@ -397,16 +601,40 @@
     <t>999961986</t>
   </si>
   <si>
+    <t>atone13sdqfpxsal48xlmspyg2dzteyqu04dvex628wa</t>
+  </si>
+  <si>
+    <t>469951548</t>
+  </si>
+  <si>
+    <t>atone13jkhp3gp2enyhnp54txq8w5aw77aaqzyvppw8y</t>
+  </si>
+  <si>
+    <t>300065984</t>
+  </si>
+  <si>
+    <t>atone135vz559nhcmvyta9y5juee8fs949nc8c7k67yr</t>
+  </si>
+  <si>
+    <t>300080377</t>
+  </si>
+  <si>
     <t>atone1jfwp4d5mg93sapd67r4274f8y8tg4xn768d2cz</t>
   </si>
   <si>
-    <t>358468451</t>
+    <t>370256909</t>
+  </si>
+  <si>
+    <t>atone1jttdtq9ah54rawwtsapt225unp8fdpedw5rzlj</t>
+  </si>
+  <si>
+    <t>2128045398</t>
   </si>
   <si>
     <t>atone1jtustv4ghy997d6catge3mgklszkvve6uhm576</t>
   </si>
   <si>
-    <t>706100000</t>
+    <t>1285979541</t>
   </si>
   <si>
     <t>atone1jujullnrumr8mplckscuxzfnzkspfm6lfjncpt</t>
@@ -415,9 +643,6 @@
     <t>atone1npurzcjvq9rd29k29atvxd90732z4lwml7ft4e</t>
   </si>
   <si>
-    <t>1000000000</t>
-  </si>
-  <si>
     <t>atone1npu9lyaf0ve5hrr30xdc8r57jje98tu5ljgw62</t>
   </si>
   <si>
@@ -433,7 +658,13 @@
     <t>atone1nf5f04rk9t56pzdwve6rhe5gvneq6gvkhscwk7</t>
   </si>
   <si>
-    <t>558241609</t>
+    <t>617905596</t>
+  </si>
+  <si>
+    <t>atone1njqpx444qvmq9q9yewupn4nztmsfzvcts3h7qj</t>
+  </si>
+  <si>
+    <t>1000004414</t>
   </si>
   <si>
     <t>atone1n45t2sknp6gjj85f25sazprq7q8kyweqv4lc0n</t>
@@ -442,12 +673,6 @@
     <t>7521345388</t>
   </si>
   <si>
-    <t>atone15plqyst4mg0tz7mgdjglleztv54rm887mdx8n5</t>
-  </si>
-  <si>
-    <t>276107194</t>
-  </si>
-  <si>
     <t>atone15rgk9gkgc0rfsflyh6ygkcn8vnnhnq49arvcdg</t>
   </si>
   <si>
@@ -457,13 +682,7 @@
     <t>atone15gq8zpzagw6e5gzed8pfggsyvjdfmsss3l22dr</t>
   </si>
   <si>
-    <t>39248247074</t>
-  </si>
-  <si>
-    <t>atone15wdtw54qpamprk4g4ea0w7elmhl9mhcva90alm</t>
-  </si>
-  <si>
-    <t>407740000</t>
+    <t>55000008383</t>
   </si>
   <si>
     <t>atone150q6ppu366x468pkhm7zcw7jk5jegg0swa8dn2</t>
@@ -484,28 +703,64 @@
     <t>67253427190</t>
   </si>
   <si>
+    <t>atone15epp26pl7cxhq6ff882cluyfxacj8lv5glcxr6</t>
+  </si>
+  <si>
+    <t>210000000</t>
+  </si>
+  <si>
     <t>atone157qu9jpq3pasuc9s50tpd4hwu3tm45lrhs7vx4</t>
   </si>
   <si>
     <t>605000000</t>
   </si>
   <si>
+    <t>atone148whzgrgd57wak0lk5teamngwww66amzc3wul8</t>
+  </si>
+  <si>
+    <t>374632881</t>
+  </si>
+  <si>
     <t>atone14f5vpj2hdw37rng9zct7llkqax2znrhyg4vg84</t>
   </si>
   <si>
-    <t>258262254</t>
+    <t>284932859</t>
+  </si>
+  <si>
+    <t>atone147vq8se2xg7nq566udrn6gz2pz9y88m7ulnvea</t>
+  </si>
+  <si>
+    <t>468938520</t>
+  </si>
+  <si>
+    <t>atone1kzyz6wyvt6maafq3ajy30ed9gxv9etwq7cv2jl</t>
+  </si>
+  <si>
+    <t>469000987</t>
   </si>
   <si>
     <t>atone1ky4l8why7jctxpwwxwy2en5txagy8j7x5kpc8n</t>
   </si>
   <si>
-    <t>440989685</t>
+    <t>3500234400</t>
+  </si>
+  <si>
+    <t>atone1kgce2j9uepahgug8c8c6vmxevhmmux7smltu7v</t>
+  </si>
+  <si>
+    <t>871927809</t>
+  </si>
+  <si>
+    <t>atone1kvq4n4n4x3gqlyfr672pjyqn73c2hdkue6lgaz</t>
+  </si>
+  <si>
+    <t>613000000</t>
   </si>
   <si>
     <t>atone1kal8h32wluskjd7gsqze9jlvk4zw7jp3fhq4l5</t>
   </si>
   <si>
-    <t>1864569984</t>
+    <t>2052855913</t>
   </si>
   <si>
     <t>atone1hv4rlv94dwwsj3z7l6muye6ndmup0htacx6m3t</t>
@@ -532,21 +787,39 @@
     <t>atone1h4x2tx4679zjv77uet0x6e6v33dc8l82kgtzvx</t>
   </si>
   <si>
+    <t>atone1h6e82vzacz2a2ewyr8rsu5hwtchvp225ypqtvu</t>
+  </si>
+  <si>
+    <t>1996915246</t>
+  </si>
+  <si>
+    <t>atone1hlfy3cmznkzu75208e7kgy4u6juk4v8y36mz0e</t>
+  </si>
+  <si>
+    <t>1000006655</t>
+  </si>
+  <si>
     <t>atone1cqrky3t78np3a60kmdpylzyv594muagf04t72v</t>
   </si>
   <si>
-    <t>502890201</t>
+    <t>276711975</t>
   </si>
   <si>
     <t>atone1cyhtq6e9x7f2haf6rn5l08svmhsrcqlvlkxzf6</t>
   </si>
   <si>
-    <t>3000000000</t>
+    <t>5000000000</t>
   </si>
   <si>
     <t>atone1cgdty3246mz7jatqkg36h2aeqwnwf2m62hm7hv</t>
   </si>
   <si>
+    <t>atone1c2gdsuq2n7avgwc7ev0puydzlk44uj5jk303wj</t>
+  </si>
+  <si>
+    <t>1000006647</t>
+  </si>
+  <si>
     <t>atone1cthyr8req6svmza3euykd2sf5pzse6z2xk3dsz</t>
   </si>
   <si>
@@ -559,10 +832,22 @@
     <t>999963509</t>
   </si>
   <si>
+    <t>atone1cjnc8hlw4gt2p8wydxjdpckywlux327nuc8wtx</t>
+  </si>
+  <si>
+    <t>400631190</t>
+  </si>
+  <si>
+    <t>atone1ccy0709lrhjfu7cg7xtyvp009d70y3zxgc9nn9</t>
+  </si>
+  <si>
+    <t>245500000</t>
+  </si>
+  <si>
     <t>atone1c7pn0kv2x784cujvthxh5km8xxuftf85angsts</t>
   </si>
   <si>
-    <t>676373988</t>
+    <t>1000468536</t>
   </si>
   <si>
     <t>atone1ezr0cxsyt4qtsm2dd4ce50kdlps8w7wars8zrh</t>
@@ -571,46 +856,79 @@
     <t>11000000000</t>
   </si>
   <si>
+    <t>atone1e0d0daqr34t7kgdumgrlrwf7xye9alqfu20hkl</t>
+  </si>
+  <si>
+    <t>6300000000</t>
+  </si>
+  <si>
+    <t>atone1e04kh9g0gdst6374grqld9mvs2lvk3tcaexysm</t>
+  </si>
+  <si>
+    <t>200000000</t>
+  </si>
+  <si>
+    <t>atone1ejskt8erpgnpzymf2js47rtnfxramr5aw2egkx</t>
+  </si>
+  <si>
     <t>atone1eewlz3pl8rhs083nqrds45kfg93sm7vu7jafhk</t>
   </si>
   <si>
-    <t>206253752</t>
+    <t>227081317</t>
   </si>
   <si>
     <t>atone1eujlkkfsyjf28ey9vce3yp0s0mdd0l94z7lxln</t>
   </si>
   <si>
+    <t>710000000</t>
+  </si>
+  <si>
+    <t>atone16pnm0sxpta3t9u7s9ujd7lkhxhdha05tafc93s</t>
+  </si>
+  <si>
+    <t>2942439382</t>
+  </si>
+  <si>
     <t>atone16yzm6qjjheafnyvlcjxnkmhj3hullgpl8u85xj</t>
   </si>
   <si>
-    <t>558017688</t>
+    <t>617910818</t>
   </si>
   <si>
     <t>atone16tfjyefrgekf0l8zzccjy2c72nh2mscjvt8pxu</t>
   </si>
   <si>
-    <t>558187461</t>
+    <t>618086776</t>
   </si>
   <si>
     <t>atone16wpn0gwepdalz0fnlq5nfy645wmwej2ctqmvyp</t>
   </si>
   <si>
-    <t>676391389</t>
+    <t>1000007269</t>
   </si>
   <si>
     <t>atone1602cse30jdmctgque3j8lc78w2frxzhnga4m5x</t>
   </si>
   <si>
+    <t>287000000</t>
+  </si>
+  <si>
     <t>atone16j9m4s9hvz2ns2z6fk2s35egca5l6rw9rjupm8</t>
   </si>
   <si>
-    <t>528814172</t>
+    <t>1001944920</t>
   </si>
   <si>
     <t>atone166au0wp40n0p0yrj7vf9gce7yre3wyq0f7nmek</t>
   </si>
   <si>
-    <t>10776968125</t>
+    <t>11865246328</t>
+  </si>
+  <si>
+    <t>atone1m846wav7usstl6upmj377k8q9zmvk3jwzhurex</t>
+  </si>
+  <si>
+    <t>1000025006</t>
   </si>
   <si>
     <t>atone1mfq9n8ghfxga047m97wuvzp5t8t7ujxrmuwwzr</t>
@@ -634,37 +952,61 @@
     <t>atone1mhkuzfws4xgcpkq252nv22vtdk93j3xdyjt28l</t>
   </si>
   <si>
-    <t>215000000</t>
+    <t>235000000</t>
   </si>
   <si>
     <t>atone1uznr6lmlyx66er4dvw54c7e25pyr0qg3at2q67</t>
   </si>
   <si>
-    <t>1999964711</t>
+    <t>2000420178</t>
+  </si>
+  <si>
+    <t>atone1ujepumwuauf5dv4jjc686f6xj4u29rtps0f5j6</t>
+  </si>
+  <si>
+    <t>2021268977</t>
   </si>
   <si>
     <t>atone1ukt0nsy3drwzmm08ane6zarvmjpts27p0cxdls</t>
   </si>
   <si>
-    <t>239339339</t>
+    <t>263508350</t>
   </si>
   <si>
     <t>atone1ucnzn86zszgjg8umz7ujzqvrcryxu46wjm3pfh</t>
   </si>
   <si>
-    <t>211000000</t>
+    <t>230000000</t>
   </si>
   <si>
     <t>atone1uey077ygnn8zz78ce9g05vkzetf32er4vg50hj</t>
   </si>
   <si>
-    <t>230968838</t>
+    <t>260417022</t>
+  </si>
+  <si>
+    <t>atone1uavz6gkj7j75ek0sxd7cue6v8vkzzjtlv4cmrp</t>
+  </si>
+  <si>
+    <t>1000448364</t>
+  </si>
+  <si>
+    <t>atone1agqxzl2r9rn6xhpjlsn3g0xf55ap687va0lt0e</t>
+  </si>
+  <si>
+    <t>469639573</t>
+  </si>
+  <si>
+    <t>atone1atasr6jurjqc9gjpy2cm0rvrwculkcqrxufa22</t>
+  </si>
+  <si>
+    <t>337000000</t>
   </si>
   <si>
     <t>atone1a3858f250ve4t6rp9ef2svpr7sj20aaxwlg6yk</t>
   </si>
   <si>
-    <t>211071708</t>
+    <t>258588237</t>
   </si>
   <si>
     <t>atone17prz2ww2r89w8ds3nhjt32lf7rwu37enzh3tac</t>
@@ -673,7 +1015,7 @@
     <t>atone17zhqvql2khzue6kpmgmd9gz5m02j67vr53n24t</t>
   </si>
   <si>
-    <t>631614698</t>
+    <t>680955641</t>
   </si>
   <si>
     <t>atone17yf8hsgezzhtl58gp3sqe7dcsj2wpqtzla05kh</t>
@@ -682,34 +1024,40 @@
     <t>2600000000</t>
   </si>
   <si>
+    <t>atone17w500e4efj3z8cu82ep5vt79ztszt9y3y2r5xh</t>
+  </si>
+  <si>
+    <t>302367229</t>
+  </si>
+  <si>
     <t>atone17hr0kwjgklazhufht4sdpllmvm6047wd66z6s5</t>
   </si>
   <si>
-    <t>503005884</t>
+    <t>275632342</t>
   </si>
   <si>
     <t>atone1lx2zuc7ls0rw0jf89y9366fg7w5l9clgu74lj3</t>
   </si>
   <si>
-    <t>300382203</t>
+    <t>468382203</t>
   </si>
   <si>
     <t>atone1lx0my7kk7uy75y68r602ga62l7n8cwawxv8gts</t>
   </si>
   <si>
-    <t>429228324</t>
+    <t>512403227</t>
   </si>
   <si>
     <t>atone1lft50ldy04u3szywhg38cnfpxfg7r548cx5ygl</t>
   </si>
   <si>
-    <t>2005185008</t>
+    <t>1588480361</t>
   </si>
   <si>
     <t>atone1l2u72c838qe5yc2mn90an2cuqddehflm4hr07k</t>
   </si>
   <si>
-    <t>502418267</t>
+    <t>554979322</t>
   </si>
   <si>
     <t>atone1ltdzw90gmtjslllkxz3a8mhw3lqyfuarl8z3vs</t>
@@ -721,13 +1069,16 @@
     <t>atone1l0tdzdyxsayestm8lu95xehgtc0s825pmq5rx5</t>
   </si>
   <si>
-    <t>10219237237</t>
+    <t>11251229084</t>
+  </si>
+  <si>
+    <t>atone1l4tw22eqltq70x2rmxgwcp99tg30kezmt9mapf</t>
   </si>
   <si>
     <t>atone1lul42lw2p4mv2mlte89cf4qnfg2jfduuz9syur</t>
   </si>
   <si>
-    <t>1287000000</t>
+    <t>1328882959</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B125"/>
+  <dimension ref="A1:B186"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -1219,207 +1570,207 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
         <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
         <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
         <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
         <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
         <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" t="s">
         <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
         <v>48</v>
-      </c>
-      <c r="B25" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
         <v>50</v>
-      </c>
-      <c r="B26" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" t="s">
         <v>52</v>
-      </c>
-      <c r="B27" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
         <v>54</v>
-      </c>
-      <c r="B28" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
         <v>56</v>
-      </c>
-      <c r="B29" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" t="s">
         <v>58</v>
-      </c>
-      <c r="B30" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" t="s">
         <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
         <v>62</v>
-      </c>
-      <c r="B32" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" t="s">
         <v>64</v>
-      </c>
-      <c r="B33" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
         <v>66</v>
-      </c>
-      <c r="B34" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" t="s">
         <v>68</v>
-      </c>
-      <c r="B35" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" t="s">
         <v>70</v>
-      </c>
-      <c r="B36" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
         <v>72</v>
-      </c>
-      <c r="B37" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
         <v>74</v>
-      </c>
-      <c r="B38" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" t="s">
         <v>76</v>
-      </c>
-      <c r="B39" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1443,71 +1794,71 @@
         <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" t="s">
         <v>83</v>
-      </c>
-      <c r="B43" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
         <v>85</v>
-      </c>
-      <c r="B44" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" t="s">
         <v>87</v>
-      </c>
-      <c r="B45" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" t="s">
         <v>89</v>
-      </c>
-      <c r="B46" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" t="s">
         <v>91</v>
-      </c>
-      <c r="B47" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
         <v>93</v>
-      </c>
-      <c r="B48" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" t="s">
         <v>95</v>
-      </c>
-      <c r="B49" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" t="s">
         <v>97</v>
-      </c>
-      <c r="B50" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1531,199 +1882,199 @@
         <v>102</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B59" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B61" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B62" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B63" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B65" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B66" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B69" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B70" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B71" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B72" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B73" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B74" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B75" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B76" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -1755,79 +2106,79 @@
         <v>155</v>
       </c>
       <c r="B81" t="s">
-        <v>156</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>156</v>
+      </c>
+      <c r="B82" t="s">
         <v>157</v>
-      </c>
-      <c r="B82" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>158</v>
+      </c>
+      <c r="B83" t="s">
         <v>159</v>
-      </c>
-      <c r="B83" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B84" t="s">
-        <v>162</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B85" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B86" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>168</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>169</v>
+      </c>
+      <c r="B89" t="s">
         <v>170</v>
-      </c>
-      <c r="B89" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>171</v>
+      </c>
+      <c r="B90" t="s">
         <v>172</v>
-      </c>
-      <c r="B90" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -1835,23 +2186,23 @@
         <v>173</v>
       </c>
       <c r="B91" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>174</v>
+      </c>
+      <c r="B92" t="s">
         <v>175</v>
-      </c>
-      <c r="B92" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>176</v>
+      </c>
+      <c r="B93" t="s">
         <v>177</v>
-      </c>
-      <c r="B93" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -1899,95 +2250,95 @@
         <v>188</v>
       </c>
       <c r="B99" t="s">
-        <v>73</v>
+        <v>189</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B100" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B101" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B102" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B103" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B104" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B105" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B106" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B107" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B108" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B109" t="s">
-        <v>207</v>
+        <v>54</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B110" t="s">
-        <v>209</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -2027,87 +2378,575 @@
         <v>218</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>219</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B116" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B117" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B118" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B119" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B120" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B121" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B122" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B123" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B124" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B125" t="s">
-        <v>238</v>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>240</v>
+      </c>
+      <c r="B126" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>242</v>
+      </c>
+      <c r="B127" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>244</v>
+      </c>
+      <c r="B128" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>246</v>
+      </c>
+      <c r="B129" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>248</v>
+      </c>
+      <c r="B130" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>250</v>
+      </c>
+      <c r="B131" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>252</v>
+      </c>
+      <c r="B132" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>254</v>
+      </c>
+      <c r="B133" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>255</v>
+      </c>
+      <c r="B134" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>257</v>
+      </c>
+      <c r="B135" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>258</v>
+      </c>
+      <c r="B136" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>260</v>
+      </c>
+      <c r="B137" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>262</v>
+      </c>
+      <c r="B138" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>264</v>
+      </c>
+      <c r="B139" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>266</v>
+      </c>
+      <c r="B140" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>267</v>
+      </c>
+      <c r="B141" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>269</v>
+      </c>
+      <c r="B142" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>271</v>
+      </c>
+      <c r="B143" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>273</v>
+      </c>
+      <c r="B144" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>275</v>
+      </c>
+      <c r="B145" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>277</v>
+      </c>
+      <c r="B146" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>279</v>
+      </c>
+      <c r="B147" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>281</v>
+      </c>
+      <c r="B148" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>283</v>
+      </c>
+      <c r="B149" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>285</v>
+      </c>
+      <c r="B150" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>286</v>
+      </c>
+      <c r="B151" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>288</v>
+      </c>
+      <c r="B152" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>290</v>
+      </c>
+      <c r="B153" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>292</v>
+      </c>
+      <c r="B154" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>294</v>
+      </c>
+      <c r="B155" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>296</v>
+      </c>
+      <c r="B156" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>298</v>
+      </c>
+      <c r="B157" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>300</v>
+      </c>
+      <c r="B158" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>302</v>
+      </c>
+      <c r="B159" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>304</v>
+      </c>
+      <c r="B160" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>306</v>
+      </c>
+      <c r="B161" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>308</v>
+      </c>
+      <c r="B162" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>310</v>
+      </c>
+      <c r="B163" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>312</v>
+      </c>
+      <c r="B164" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>314</v>
+      </c>
+      <c r="B165" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>316</v>
+      </c>
+      <c r="B166" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>318</v>
+      </c>
+      <c r="B167" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>320</v>
+      </c>
+      <c r="B168" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>322</v>
+      </c>
+      <c r="B169" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>324</v>
+      </c>
+      <c r="B170" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>326</v>
+      </c>
+      <c r="B171" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>328</v>
+      </c>
+      <c r="B172" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>330</v>
+      </c>
+      <c r="B173" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>332</v>
+      </c>
+      <c r="B174" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>333</v>
+      </c>
+      <c r="B175" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>335</v>
+      </c>
+      <c r="B176" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>337</v>
+      </c>
+      <c r="B177" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>339</v>
+      </c>
+      <c r="B178" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>341</v>
+      </c>
+      <c r="B179" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>343</v>
+      </c>
+      <c r="B180" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>345</v>
+      </c>
+      <c r="B181" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>347</v>
+      </c>
+      <c r="B182" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>349</v>
+      </c>
+      <c r="B183" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>351</v>
+      </c>
+      <c r="B184" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>353</v>
+      </c>
+      <c r="B185" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>354</v>
+      </c>
+      <c r="B186" t="s">
+        <v>355</v>
       </c>
     </row>
   </sheetData>
